--- a/tame_output/ON/bt/strategyON_20230901.xlsx
+++ b/tame_output/ON/bt/strategyON_20230901.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.7%</t>
+          <t>101.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.5%</t>
+          <t>-158.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.6%</t>
+          <t>132.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1706"/>
+  <dimension ref="A1:G1707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40748,7 +40748,7 @@
         <v>45168</v>
       </c>
       <c r="B1706" t="n">
-        <v>2.812436797443585</v>
+        <v>2.813474724306067</v>
       </c>
       <c r="C1706" t="n">
         <v>2.896006691252195</v>
@@ -40764,6 +40764,29 @@
       </c>
       <c r="G1706" t="n">
         <v>4.196491399670214</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="2" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B1707" t="n">
+        <v>2.770405762234912</v>
+      </c>
+      <c r="C1707" t="n">
+        <v>2.891093788499763</v>
+      </c>
+      <c r="D1707" t="n">
+        <v>1.559301443061206</v>
+      </c>
+      <c r="E1707" t="n">
+        <v>3.514457941410498</v>
+      </c>
+      <c r="F1707" t="n">
+        <v>2.16740979396568</v>
+      </c>
+      <c r="G1707" t="n">
+        <v>4.191539664879173</v>
       </c>
     </row>
   </sheetData>
